--- a/VerveStacks_KEN_grids_kan10/SysSettings.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BA2272-533B-4873-B0D1-5808635D4DA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D187949-B868-4D8A-9CE7-1C813ED12FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5733,7 +5733,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C330E537-BBDB-45D5-A764-5A85B0002B8B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9333EE62-9740-4050-A4B8-D31BDD94C692}">
   <dimension ref="B3:I16"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
